--- a/production-test/files/Услуги нам.xlsx
+++ b/production-test/files/Услуги нам.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="128" documentId="11_4859B067FFD28D9FD9096DEAB40B950AE04F5FF9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9963052-F1FA-4EA7-9C0C-B14713D103A8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5C2ABE-4493-45EC-A0B1-08CCF245EFB4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Промстеклосн" sheetId="1" r:id="rId1"/>
-    <sheet name="ПЭК" sheetId="3" r:id="rId2"/>
+    <sheet name="ООО &quot;ПРОМСТЕКЛОСНАБ&quot;" sheetId="1" r:id="rId1"/>
+    <sheet name="ООО &quot;ПЭК&quot;" sheetId="3" r:id="rId2"/>
     <sheet name="ИП Козырева" sheetId="2" r:id="rId3"/>
     <sheet name="ИП Камалов" sheetId="4" r:id="rId4"/>
-    <sheet name="ИП Савин" sheetId="6" r:id="rId5"/>
-    <sheet name="Итеко России" sheetId="5" r:id="rId6"/>
-    <sheet name="ФМ логистик" sheetId="7" r:id="rId7"/>
+    <sheet name="ИП Савин Денис Валерьевич" sheetId="6" r:id="rId5"/>
+    <sheet name="ООО &quot;ИТЕКО" sheetId="5" r:id="rId6"/>
+    <sheet name="ООО &quot;ЮГ-ЛОГИСТИКА&quot;" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,9 +27,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1593,7 +1593,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9">
-        <f>I2-F3+H3</f>
+        <f t="shared" ref="I3:I34" si="0">I2-F3+H3</f>
         <v>-15000</v>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9">
-        <f>I3-F4+H4</f>
+        <f t="shared" si="0"/>
         <v>-32000</v>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       <c r="G5" s="6"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9">
-        <f>I4-F5+H5</f>
+        <f t="shared" si="0"/>
         <v>-48000</v>
       </c>
       <c r="J5" s="12"/>
@@ -1661,7 +1661,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="8"/>
       <c r="F6" s="56">
-        <f t="shared" ref="F6:F19" si="0">D6*E6</f>
+        <f t="shared" ref="F6:F19" si="1">D6*E6</f>
         <v>0</v>
       </c>
       <c r="G6" s="11">
@@ -1671,7 +1671,7 @@
         <v>144000</v>
       </c>
       <c r="I6" s="9">
-        <f>I5-F6+H6</f>
+        <f t="shared" si="0"/>
         <v>96000</v>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       <c r="G7" s="11"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9">
-        <f>I6-F7+H7</f>
+        <f t="shared" si="0"/>
         <v>81000</v>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9">
-        <f>I7-F8+H8</f>
+        <f t="shared" si="0"/>
         <v>16000</v>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9">
-        <f>I8-F9+H9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1736,13 +1736,13 @@
       <c r="D10" s="39"/>
       <c r="E10" s="40"/>
       <c r="F10" s="40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G10" s="38"/>
       <c r="H10" s="41"/>
       <c r="I10" s="41">
-        <f>I9-F10+H10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1763,13 +1763,13 @@
         <v>11000</v>
       </c>
       <c r="F11" s="132">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11000</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9">
-        <f>I10-F11+H11</f>
+        <f t="shared" si="0"/>
         <v>-11000</v>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       <c r="D12" s="53"/>
       <c r="E12" s="54"/>
       <c r="F12" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G12" s="11">
@@ -1792,7 +1792,7 @@
         <v>31000</v>
       </c>
       <c r="I12" s="9">
-        <f>I11-F12+H12</f>
+        <f t="shared" si="0"/>
         <v>20000</v>
       </c>
     </row>
@@ -1813,13 +1813,13 @@
         <v>15000</v>
       </c>
       <c r="F13" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15000</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9">
-        <f>I12-F13+H13</f>
+        <f t="shared" si="0"/>
         <v>5000</v>
       </c>
     </row>
@@ -1840,13 +1840,13 @@
         <v>32000</v>
       </c>
       <c r="F14" s="132">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32000</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9">
-        <f>I13-F14+H14</f>
+        <f t="shared" si="0"/>
         <v>-27000</v>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       <c r="G15" s="6"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9">
-        <f>I14-F15+H15</f>
+        <f t="shared" si="0"/>
         <v>-87000</v>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       <c r="G16" s="6"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9">
-        <f>I15-F16+H16</f>
+        <f t="shared" si="0"/>
         <v>-97000</v>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9">
-        <f>I16-F17+H17</f>
+        <f t="shared" si="0"/>
         <v>-108000</v>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9">
-        <f>I17-F18+H18</f>
+        <f t="shared" si="0"/>
         <v>-119000</v>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       <c r="D19" s="53"/>
       <c r="E19" s="54"/>
       <c r="F19" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G19" s="11">
@@ -1973,7 +1973,7 @@
         <v>60000</v>
       </c>
       <c r="I19" s="9">
-        <f>I18-F19+H19</f>
+        <f t="shared" si="0"/>
         <v>-59000</v>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
         <v>15552</v>
       </c>
       <c r="E20" s="54">
-        <f t="shared" ref="E20:E32" si="1">F20/D20</f>
+        <f t="shared" ref="E20:E32" si="2">F20/D20</f>
         <v>0.70730452674897115</v>
       </c>
       <c r="F20" s="132">
@@ -2000,7 +2000,7 @@
       <c r="G20" s="11"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9">
-        <f>I19-F20+H20</f>
+        <f t="shared" si="0"/>
         <v>-70000</v>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
         <v>19000</v>
       </c>
       <c r="E21" s="54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.6842105263157894</v>
       </c>
       <c r="F21" s="56">
@@ -2031,7 +2031,7 @@
         <v>32000</v>
       </c>
       <c r="I21" s="9">
-        <f>I20-F21+H21</f>
+        <f t="shared" si="0"/>
         <v>-70000</v>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
         <v>11232</v>
       </c>
       <c r="E22" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.3354700854700854</v>
       </c>
       <c r="F22" s="132">
@@ -2058,7 +2058,7 @@
       <c r="G22" s="6"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9">
-        <f>I21-F22+H22</f>
+        <f t="shared" si="0"/>
         <v>-85000</v>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
         <v>2240</v>
       </c>
       <c r="E23" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.8214285714285712</v>
       </c>
       <c r="F23" s="138">
@@ -2083,7 +2083,7 @@
       <c r="G23" s="6"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9">
-        <f>I22-F23+H23</f>
+        <f t="shared" si="0"/>
         <v>-107000</v>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>21600</v>
       </c>
       <c r="E24" s="135">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5092592592592593</v>
       </c>
       <c r="F24" s="139">
@@ -2110,7 +2110,7 @@
       <c r="G24" s="106"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9">
-        <f>I23-F24+H24</f>
+        <f t="shared" si="0"/>
         <v>-118000</v>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
         <v>490</v>
       </c>
       <c r="E25" s="136">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.244897959183673</v>
       </c>
       <c r="F25" s="140">
@@ -2135,7 +2135,7 @@
       <c r="G25" s="137"/>
       <c r="H25" s="70"/>
       <c r="I25" s="70">
-        <f>I24-F25+H25</f>
+        <f t="shared" si="0"/>
         <v>-124000</v>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
         <v>9504</v>
       </c>
       <c r="E26" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.3678451178451179</v>
       </c>
       <c r="F26" s="133">
@@ -2162,7 +2162,7 @@
       <c r="G26" s="18"/>
       <c r="H26" s="68"/>
       <c r="I26" s="68">
-        <f>I25-F26+H26</f>
+        <f t="shared" si="0"/>
         <v>-137000</v>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       <c r="D27" s="7"/>
       <c r="E27" s="8"/>
       <c r="F27" s="56">
-        <f t="shared" ref="F27:F66" si="2">C27*E27+D27*E27</f>
+        <f t="shared" ref="F27:F66" si="3">C27*E27+D27*E27</f>
         <v>0</v>
       </c>
       <c r="G27" s="11">
@@ -2183,7 +2183,7 @@
         <v>10000</v>
       </c>
       <c r="I27" s="9">
-        <f>I26-F27+H27</f>
+        <f t="shared" si="0"/>
         <v>-127000</v>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
         <v>17280</v>
       </c>
       <c r="E28" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.69444444444444442</v>
       </c>
       <c r="F28" s="134">
@@ -2210,7 +2210,7 @@
       <c r="G28" s="14"/>
       <c r="H28" s="70"/>
       <c r="I28" s="70">
-        <f>I27-F28+H28</f>
+        <f t="shared" si="0"/>
         <v>-139000</v>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
         <v>13824</v>
       </c>
       <c r="E29" s="141">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.54253472222222221</v>
       </c>
       <c r="F29" s="139">
@@ -2237,7 +2237,7 @@
       <c r="G29" s="142"/>
       <c r="H29" s="68"/>
       <c r="I29" s="68">
-        <f>I28-F29+H29</f>
+        <f t="shared" si="0"/>
         <v>-146500</v>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
         <v>1440</v>
       </c>
       <c r="E30" s="135">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.208333333333333</v>
       </c>
       <c r="F30" s="140">
@@ -2262,7 +2262,7 @@
       <c r="G30" s="106"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9">
-        <f>I29-F30+H30</f>
+        <f t="shared" si="0"/>
         <v>-154000</v>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9">
-        <f>I30-F31+H31</f>
+        <f t="shared" si="0"/>
         <v>-190000</v>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
         <v>31104</v>
       </c>
       <c r="E32" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.48225308641975306</v>
       </c>
       <c r="F32" s="132">
@@ -2315,7 +2315,7 @@
         <v>11000</v>
       </c>
       <c r="I32" s="9">
-        <f>I31-F32+H32</f>
+        <f t="shared" si="0"/>
         <v>-194000</v>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       <c r="G33" s="13"/>
       <c r="H33" s="70"/>
       <c r="I33" s="70">
-        <f>I32-F33+H33</f>
+        <f t="shared" si="0"/>
         <v>-194000</v>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       <c r="D34" s="86"/>
       <c r="E34" s="87"/>
       <c r="F34" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G34" s="88">
@@ -2358,7 +2358,7 @@
         <v>8000</v>
       </c>
       <c r="I34" s="89">
-        <f>I33-F34+H34</f>
+        <f t="shared" si="0"/>
         <v>-186000</v>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v>20736</v>
       </c>
       <c r="E35" s="8">
-        <f t="shared" ref="E35:E39" si="3">F35/D35</f>
+        <f t="shared" ref="E35:E39" si="4">F35/D35</f>
         <v>0.62692901234567899</v>
       </c>
       <c r="F35" s="138">
@@ -2385,7 +2385,7 @@
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
       <c r="I35" s="100">
-        <f>I34-F35+H35</f>
+        <f t="shared" ref="I35:I66" si="5">I34-F35+H35</f>
         <v>-199000</v>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
         <v>27648</v>
       </c>
       <c r="E36" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.54253472222222221</v>
       </c>
       <c r="F36" s="139">
@@ -2412,7 +2412,7 @@
       <c r="G36" s="106"/>
       <c r="H36" s="9"/>
       <c r="I36" s="100">
-        <f>I35-F36+H36</f>
+        <f t="shared" si="5"/>
         <v>-214000</v>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
         <v>25920</v>
       </c>
       <c r="E37" s="136">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.57870370370370372</v>
       </c>
       <c r="F37" s="140">
@@ -2437,7 +2437,7 @@
       <c r="G37" s="137"/>
       <c r="H37" s="70"/>
       <c r="I37" s="92">
-        <f>I36-F37+H37</f>
+        <f t="shared" si="5"/>
         <v>-229000</v>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       <c r="D38" s="19"/>
       <c r="E38" s="20"/>
       <c r="F38" s="67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G38" s="21">
@@ -2458,7 +2458,7 @@
         <v>22000</v>
       </c>
       <c r="I38" s="68">
-        <f>I37-F38+H38</f>
+        <f t="shared" si="5"/>
         <v>-207000</v>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
         <v>20160</v>
       </c>
       <c r="E39" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.94246031746031744</v>
       </c>
       <c r="F39" s="132">
@@ -2485,7 +2485,7 @@
       <c r="G39" s="6"/>
       <c r="H39" s="9"/>
       <c r="I39" s="9">
-        <f>I38-F39+H39</f>
+        <f t="shared" si="5"/>
         <v>-226000</v>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
         <v>5000</v>
       </c>
       <c r="E40" s="8">
-        <f t="shared" ref="E40" si="4">F40/D40</f>
+        <f t="shared" ref="E40" si="6">F40/D40</f>
         <v>5</v>
       </c>
       <c r="F40" s="132">
@@ -2510,7 +2510,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="9"/>
       <c r="I40" s="9">
-        <f>I39-F40+H40</f>
+        <f t="shared" si="5"/>
         <v>-251000</v>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       <c r="D41" s="7"/>
       <c r="E41" s="20"/>
       <c r="F41" s="56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G41" s="11">
@@ -2531,7 +2531,7 @@
         <v>26000</v>
       </c>
       <c r="I41" s="9">
-        <f>I40-F41+H41</f>
+        <f t="shared" si="5"/>
         <v>-225000</v>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       <c r="D42" s="75"/>
       <c r="E42" s="76"/>
       <c r="F42" s="76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G42" s="74"/>
@@ -2554,7 +2554,7 @@
         <v>-38000</v>
       </c>
       <c r="I42" s="77">
-        <f>I41-F42+H42</f>
+        <f t="shared" si="5"/>
         <v>-263000</v>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       <c r="D43" s="86"/>
       <c r="E43" s="87"/>
       <c r="F43" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G43" s="88">
@@ -2577,7 +2577,7 @@
         <v>22000</v>
       </c>
       <c r="I43" s="89">
-        <f>I42-F43+H43</f>
+        <f t="shared" si="5"/>
         <v>-241000</v>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
         <v>20160</v>
       </c>
       <c r="E44" s="16">
-        <f t="shared" ref="E44:E47" si="5">F44/D44</f>
+        <f t="shared" ref="E44:E47" si="7">F44/D44</f>
         <v>0.94246031746031744</v>
       </c>
       <c r="F44" s="69">
@@ -2604,7 +2604,7 @@
       <c r="G44" s="14"/>
       <c r="H44" s="70"/>
       <c r="I44" s="92">
-        <f>I43-F44+H44</f>
+        <f t="shared" si="5"/>
         <v>-260000</v>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
         <v>7200</v>
       </c>
       <c r="E45" s="87">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="F45" s="120">
@@ -2635,7 +2635,7 @@
         <v>49000</v>
       </c>
       <c r="I45" s="89">
-        <f>I44-F45+H45</f>
+        <f t="shared" si="5"/>
         <v>-223000</v>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>14000</v>
       </c>
       <c r="E46" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.2857142857142856</v>
       </c>
       <c r="F46" s="56">
@@ -2662,7 +2662,7 @@
       <c r="G46" s="11"/>
       <c r="H46" s="9"/>
       <c r="I46" s="100">
-        <f>I45-F46+H46</f>
+        <f t="shared" si="5"/>
         <v>-255000</v>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
         <v>5000</v>
       </c>
       <c r="E47" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="F47" s="56">
@@ -2689,7 +2689,7 @@
       <c r="G47" s="11"/>
       <c r="H47" s="9"/>
       <c r="I47" s="100">
-        <f>I46-F47+H47</f>
+        <f t="shared" si="5"/>
         <v>-275000</v>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       <c r="D48" s="7"/>
       <c r="E48" s="8"/>
       <c r="F48" s="56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G48" s="11">
@@ -2710,7 +2710,7 @@
         <v>25000</v>
       </c>
       <c r="I48" s="100">
-        <f>I47-F48+H48</f>
+        <f t="shared" si="5"/>
         <v>-250000</v>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
       <c r="F49" s="56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G49" s="11">
@@ -2731,7 +2731,7 @@
         <v>15000</v>
       </c>
       <c r="I49" s="100">
-        <f>I48-F49+H49</f>
+        <f t="shared" si="5"/>
         <v>-235000</v>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
         <v>43200</v>
       </c>
       <c r="E50" s="16">
-        <f t="shared" ref="E50" si="6">F50/D50</f>
+        <f t="shared" ref="E50" si="8">F50/D50</f>
         <v>0.67129629629629628</v>
       </c>
       <c r="F50" s="69">
@@ -2762,7 +2762,7 @@
         <v>17000</v>
       </c>
       <c r="I50" s="92">
-        <f>I49-F50+H50</f>
+        <f t="shared" si="5"/>
         <v>-247000</v>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       <c r="D51" s="86"/>
       <c r="E51" s="87"/>
       <c r="F51" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G51" s="88">
@@ -2783,7 +2783,7 @@
         <v>43000</v>
       </c>
       <c r="I51" s="89">
-        <f>I50-F51+H51</f>
+        <f t="shared" si="5"/>
         <v>-204000</v>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       <c r="G52" s="6"/>
       <c r="H52" s="9"/>
       <c r="I52" s="100">
-        <f>I51-F52+H52</f>
+        <f t="shared" si="5"/>
         <v>-222000</v>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       <c r="G53" s="6"/>
       <c r="H53" s="9"/>
       <c r="I53" s="100">
-        <f>I52-F53+H53</f>
+        <f t="shared" si="5"/>
         <v>-242000</v>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
         <v>10080</v>
       </c>
       <c r="E54" s="8">
-        <f t="shared" ref="E54:E55" si="7">F54/D54</f>
+        <f t="shared" ref="E54:E55" si="9">F54/D54</f>
         <v>1.3888888888888888</v>
       </c>
       <c r="F54" s="56">
@@ -2852,7 +2852,7 @@
       <c r="G54" s="6"/>
       <c r="H54" s="9"/>
       <c r="I54" s="100">
-        <f>I53-F54+H54</f>
+        <f t="shared" si="5"/>
         <v>-256000</v>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
         <v>20000</v>
       </c>
       <c r="E55" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2.5</v>
       </c>
       <c r="F55" s="69">
@@ -2877,7 +2877,7 @@
       <c r="G55" s="14"/>
       <c r="H55" s="70"/>
       <c r="I55" s="92">
-        <f>I54-F55+H55</f>
+        <f t="shared" si="5"/>
         <v>-306000</v>
       </c>
     </row>
@@ -2888,13 +2888,13 @@
       <c r="D56" s="116"/>
       <c r="E56" s="117"/>
       <c r="F56" s="117">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G56" s="115"/>
       <c r="H56" s="118"/>
       <c r="I56" s="118">
-        <f>I55-F56+H56</f>
+        <f t="shared" si="5"/>
         <v>-306000</v>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
       <c r="F57" s="56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G57" s="11">
@@ -2917,7 +2917,7 @@
         <v>44000</v>
       </c>
       <c r="I57" s="9">
-        <f>I56-F57+H57</f>
+        <f t="shared" si="5"/>
         <v>-262000</v>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
         <v>5000</v>
       </c>
       <c r="E58" s="8">
-        <f t="shared" ref="E58:E59" si="8">F58/D58</f>
+        <f t="shared" ref="E58:E59" si="10">F58/D58</f>
         <v>3.8</v>
       </c>
       <c r="F58" s="56">
@@ -2944,7 +2944,7 @@
       <c r="G58" s="6"/>
       <c r="H58" s="9"/>
       <c r="I58" s="9">
-        <f>I57-F58+H58</f>
+        <f t="shared" si="5"/>
         <v>-281000</v>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
         <v>11520</v>
       </c>
       <c r="E59" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1.2152777777777777</v>
       </c>
       <c r="F59" s="56">
@@ -2971,7 +2971,7 @@
       <c r="G59" s="6"/>
       <c r="H59" s="9"/>
       <c r="I59" s="9">
-        <f>I58-F59+H59</f>
+        <f t="shared" si="5"/>
         <v>-295000</v>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
         <v>64000</v>
       </c>
       <c r="I60" s="9">
-        <f>I59-F60+H60</f>
+        <f t="shared" si="5"/>
         <v>-247000</v>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
         <v>52000</v>
       </c>
       <c r="I61" s="9">
-        <f>I60-F61+H61</f>
+        <f t="shared" si="5"/>
         <v>-595000</v>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
         <v>29000</v>
       </c>
       <c r="I62" s="9">
-        <f>I61-F62+H62</f>
+        <f t="shared" si="5"/>
         <v>-566000</v>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
       <c r="F63" s="56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G63" s="6" t="s">
@@ -3058,7 +3058,7 @@
         <v>20000</v>
       </c>
       <c r="I63" s="9">
-        <f>I62-F63+H63</f>
+        <f t="shared" si="5"/>
         <v>-546000</v>
       </c>
     </row>
@@ -3069,13 +3069,13 @@
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
       <c r="F64" s="56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G64" s="6"/>
       <c r="H64" s="9"/>
       <c r="I64" s="9">
-        <f>I63-F64+H64</f>
+        <f t="shared" si="5"/>
         <v>-546000</v>
       </c>
     </row>
@@ -3086,13 +3086,13 @@
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
       <c r="F65" s="56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G65" s="6"/>
       <c r="H65" s="9"/>
       <c r="I65" s="9">
-        <f>I64-F65+H65</f>
+        <f t="shared" si="5"/>
         <v>-546000</v>
       </c>
     </row>
@@ -3103,13 +3103,13 @@
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
       <c r="F66" s="56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G66" s="6"/>
       <c r="H66" s="9"/>
       <c r="I66" s="9">
-        <f>I65-F66+H66</f>
+        <f t="shared" si="5"/>
         <v>-546000</v>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
         <v>17081.66</v>
       </c>
       <c r="I3" s="9">
-        <f>I2-F3+H3</f>
+        <f t="shared" ref="I3:I34" si="0">I2-F3+H3</f>
         <v>17081.66</v>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="8"/>
       <c r="I4" s="9">
-        <f>I3-F4+H4</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       <c r="G5" s="38"/>
       <c r="H5" s="40"/>
       <c r="I5" s="41">
-        <f>I4-F5+H5</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
       <c r="J5" s="12"/>
@@ -3265,13 +3265,13 @@
       <c r="D6" s="7"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8">
-        <f t="shared" ref="F6:F23" si="0">D6*E6</f>
+        <f t="shared" ref="F6:F23" si="1">D6*E6</f>
         <v>0</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="8"/>
       <c r="I6" s="9">
-        <f>I5-F6+H6</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
       <c r="D7" s="7"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="8"/>
       <c r="I7" s="9">
-        <f>I6-F7+H7</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3299,13 +3299,13 @@
       <c r="D8" s="7"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="8"/>
       <c r="I8" s="9">
-        <f>I7-F8+H8</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3316,13 +3316,13 @@
       <c r="D9" s="7"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="8"/>
       <c r="I9" s="9">
-        <f>I8-F9+H9</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3333,13 +3333,13 @@
       <c r="D10" s="7"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="8"/>
       <c r="I10" s="9">
-        <f>I9-F10+H10</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3350,13 +3350,13 @@
       <c r="D11" s="7"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="8"/>
       <c r="I11" s="9">
-        <f>I10-F11+H11</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3367,13 +3367,13 @@
       <c r="D12" s="7"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="8"/>
       <c r="I12" s="9">
-        <f>I11-F12+H12</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3384,13 +3384,13 @@
       <c r="D13" s="7"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="8"/>
       <c r="I13" s="9">
-        <f>I12-F13+H13</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3401,13 +3401,13 @@
       <c r="D14" s="7"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="8"/>
       <c r="I14" s="9">
-        <f>I13-F14+H14</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3418,13 +3418,13 @@
       <c r="D15" s="15"/>
       <c r="E15" s="16"/>
       <c r="F15" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="16"/>
       <c r="I15" s="9">
-        <f>I14-F15+H15</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3435,13 +3435,13 @@
       <c r="D16" s="19"/>
       <c r="E16" s="20"/>
       <c r="F16" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="20"/>
       <c r="I16" s="9">
-        <f>I15-F16+H16</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3452,13 +3452,13 @@
       <c r="D17" s="7"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="8"/>
       <c r="I17" s="9">
-        <f>I16-F17+H17</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3469,13 +3469,13 @@
       <c r="D18" s="7"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="8"/>
       <c r="I18" s="9">
-        <f>I17-F18+H18</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3486,13 +3486,13 @@
       <c r="D19" s="7"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="8"/>
       <c r="I19" s="9">
-        <f>I18-F19+H19</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3503,13 +3503,13 @@
       <c r="D20" s="7"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="8"/>
       <c r="I20" s="9">
-        <f>I19-F20+H20</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3520,13 +3520,13 @@
       <c r="D21" s="7"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="8"/>
       <c r="I21" s="9">
-        <f>I20-F21+H21</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3537,13 +3537,13 @@
       <c r="D22" s="7"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="8"/>
       <c r="I22" s="9">
-        <f>I21-F22+H22</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3554,13 +3554,13 @@
       <c r="D23" s="7"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="8"/>
       <c r="I23" s="9">
-        <f>I22-F23+H23</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3571,13 +3571,13 @@
       <c r="D24" s="7"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8">
-        <f t="shared" ref="F24:F56" si="1">C24*E24+D24*E24</f>
+        <f t="shared" ref="F24:F56" si="2">C24*E24+D24*E24</f>
         <v>0</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="8"/>
       <c r="I24" s="9">
-        <f>I23-F24+H24</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3588,13 +3588,13 @@
       <c r="D25" s="7"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="8"/>
       <c r="I25" s="9">
-        <f>I24-F25+H25</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3605,13 +3605,13 @@
       <c r="D26" s="7"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="8"/>
       <c r="I26" s="9">
-        <f>I25-F26+H26</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3622,13 +3622,13 @@
       <c r="D27" s="7"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="8"/>
       <c r="I27" s="9">
-        <f>I26-F27+H27</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3639,13 +3639,13 @@
       <c r="D28" s="7"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="8"/>
       <c r="I28" s="9">
-        <f>I27-F28+H28</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3656,13 +3656,13 @@
       <c r="D29" s="7"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="8"/>
       <c r="I29" s="9">
-        <f>I28-F29+H29</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3673,13 +3673,13 @@
       <c r="D30" s="7"/>
       <c r="E30" s="8"/>
       <c r="F30" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="8"/>
       <c r="I30" s="9">
-        <f>I29-F30+H30</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3690,13 +3690,13 @@
       <c r="D31" s="7"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="8"/>
       <c r="I31" s="9">
-        <f>I30-F31+H31</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3707,13 +3707,13 @@
       <c r="D32" s="7"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="8"/>
       <c r="I32" s="9">
-        <f>I31-F32+H32</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3724,13 +3724,13 @@
       <c r="D33" s="7"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="8"/>
       <c r="I33" s="9">
-        <f>I32-F33+H33</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3741,13 +3741,13 @@
       <c r="D34" s="7"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="8"/>
       <c r="I34" s="9">
-        <f>I33-F34+H34</f>
+        <f t="shared" si="0"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3758,13 +3758,13 @@
       <c r="D35" s="7"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9">
-        <f>I34-F35+H35</f>
+        <f t="shared" ref="I35:I66" si="3">I34-F35+H35</f>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3775,13 +3775,13 @@
       <c r="D36" s="7"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="8"/>
       <c r="I36" s="9">
-        <f>I35-F36+H36</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3792,13 +3792,13 @@
       <c r="D37" s="7"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="8"/>
       <c r="I37" s="9">
-        <f>I36-F37+H37</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3809,13 +3809,13 @@
       <c r="D38" s="7"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9">
-        <f>I37-F38+H38</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3826,13 +3826,13 @@
       <c r="D39" s="7"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9">
-        <f>I38-F39+H39</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3843,13 +3843,13 @@
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9">
-        <f>I39-F40+H40</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3860,13 +3860,13 @@
       <c r="D41" s="7"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9">
-        <f>I40-F41+H41</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3877,13 +3877,13 @@
       <c r="D42" s="15"/>
       <c r="E42" s="16"/>
       <c r="F42" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G42" s="14"/>
       <c r="H42" s="16"/>
       <c r="I42" s="9">
-        <f>I41-F42+H42</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3894,13 +3894,13 @@
       <c r="D43" s="19"/>
       <c r="E43" s="20"/>
       <c r="F43" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G43" s="18"/>
       <c r="H43" s="20"/>
       <c r="I43" s="9">
-        <f>I42-F43+H43</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3911,13 +3911,13 @@
       <c r="D44" s="7"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="8"/>
       <c r="I44" s="9">
-        <f>I43-F44+H44</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3928,13 +3928,13 @@
       <c r="D45" s="7"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G45" s="11"/>
       <c r="H45" s="8"/>
       <c r="I45" s="9">
-        <f>I44-F45+H45</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3945,13 +3945,13 @@
       <c r="D46" s="7"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="8"/>
       <c r="I46" s="9">
-        <f>I45-F46+H46</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3962,13 +3962,13 @@
       <c r="D47" s="7"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="8"/>
       <c r="I47" s="9">
-        <f>I46-F47+H47</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D48" s="7"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="8"/>
       <c r="I48" s="9">
-        <f>I47-F48+H48</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -3996,13 +3996,13 @@
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="8"/>
       <c r="I49" s="9">
-        <f>I48-F49+H49</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -4013,13 +4013,13 @@
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="8"/>
       <c r="I50" s="9">
-        <f>I49-F50+H50</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -4030,13 +4030,13 @@
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="8"/>
       <c r="I51" s="9">
-        <f>I50-F51+H51</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -4047,13 +4047,13 @@
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="8"/>
       <c r="I52" s="9">
-        <f>I51-F52+H52</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -4064,13 +4064,13 @@
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="8"/>
       <c r="I53" s="9">
-        <f>I52-F53+H53</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -4081,13 +4081,13 @@
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="8"/>
       <c r="I54" s="9">
-        <f>I53-F54+H54</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -4098,13 +4098,13 @@
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="8"/>
       <c r="I55" s="9">
-        <f>I54-F55+H55</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -4115,13 +4115,13 @@
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="8"/>
       <c r="I56" s="9">
-        <f>I55-F56+H56</f>
+        <f t="shared" si="3"/>
         <v>3908.6601599999995</v>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
         <v>20000</v>
       </c>
       <c r="I3" s="9">
-        <f>I2-F3+H3</f>
+        <f t="shared" ref="I3:I34" si="0">I2-F3+H3</f>
         <v>20000</v>
       </c>
     </row>
@@ -4245,7 +4245,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="9">
-        <f>I3-F4+H4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="9">
-        <f>I4-F5+H5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J5" s="12"/>
@@ -4274,13 +4274,13 @@
       <c r="D6" s="7"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8">
-        <f t="shared" ref="F6:F23" si="0">D6*E6</f>
+        <f t="shared" ref="F6:F23" si="1">D6*E6</f>
         <v>0</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="6"/>
       <c r="I6" s="9">
-        <f>I5-F6+H6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4291,13 +4291,13 @@
       <c r="D7" s="7"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="9">
-        <f>I6-F7+H7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4308,13 +4308,13 @@
       <c r="D8" s="7"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="9">
-        <f>I7-F8+H8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4325,13 +4325,13 @@
       <c r="D9" s="7"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="9">
-        <f>I8-F9+H9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4342,13 +4342,13 @@
       <c r="D10" s="7"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="9">
-        <f>I9-F10+H10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4359,13 +4359,13 @@
       <c r="D11" s="7"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="9">
-        <f>I10-F11+H11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4376,13 +4376,13 @@
       <c r="D12" s="7"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="9">
-        <f>I11-F12+H12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4393,13 +4393,13 @@
       <c r="D13" s="7"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="9">
-        <f>I12-F13+H13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4410,13 +4410,13 @@
       <c r="D14" s="7"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="9">
-        <f>I13-F14+H14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4427,13 +4427,13 @@
       <c r="D15" s="15"/>
       <c r="E15" s="16"/>
       <c r="F15" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="14"/>
       <c r="I15" s="9">
-        <f>I14-F15+H15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4444,13 +4444,13 @@
       <c r="D16" s="19"/>
       <c r="E16" s="20"/>
       <c r="F16" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
       <c r="I16" s="9">
-        <f>I15-F16+H16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4461,13 +4461,13 @@
       <c r="D17" s="7"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="9">
-        <f>I16-F17+H17</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4478,13 +4478,13 @@
       <c r="D18" s="7"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="9">
-        <f>I17-F18+H18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4495,13 +4495,13 @@
       <c r="D19" s="7"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="6"/>
       <c r="I19" s="9">
-        <f>I18-F19+H19</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4512,13 +4512,13 @@
       <c r="D20" s="7"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="6"/>
       <c r="I20" s="9">
-        <f>I19-F20+H20</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4529,13 +4529,13 @@
       <c r="D21" s="7"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="9">
-        <f>I20-F21+H21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4546,13 +4546,13 @@
       <c r="D22" s="7"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="9">
-        <f>I21-F22+H22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4563,13 +4563,13 @@
       <c r="D23" s="7"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="9">
-        <f>I22-F23+H23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4580,13 +4580,13 @@
       <c r="D24" s="7"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8">
-        <f t="shared" ref="F24:F56" si="1">C24*E24+D24*E24</f>
+        <f t="shared" ref="F24:F56" si="2">C24*E24+D24*E24</f>
         <v>0</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="9">
-        <f>I23-F24+H24</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4597,13 +4597,13 @@
       <c r="D25" s="7"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="9">
-        <f>I24-F25+H25</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4614,13 +4614,13 @@
       <c r="D26" s="7"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="9">
-        <f>I25-F26+H26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4631,13 +4631,13 @@
       <c r="D27" s="7"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="9">
-        <f>I26-F27+H27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4648,13 +4648,13 @@
       <c r="D28" s="7"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="9">
-        <f>I27-F28+H28</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4665,13 +4665,13 @@
       <c r="D29" s="7"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="9">
-        <f>I28-F29+H29</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4682,13 +4682,13 @@
       <c r="D30" s="7"/>
       <c r="E30" s="8"/>
       <c r="F30" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="9">
-        <f>I29-F30+H30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4699,13 +4699,13 @@
       <c r="D31" s="7"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="6"/>
       <c r="I31" s="9">
-        <f>I30-F31+H31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4716,13 +4716,13 @@
       <c r="D32" s="7"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="9">
-        <f>I31-F32+H32</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4733,13 +4733,13 @@
       <c r="D33" s="7"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="9">
-        <f>I32-F33+H33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4750,13 +4750,13 @@
       <c r="D34" s="7"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="9">
-        <f>I33-F34+H34</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4767,13 +4767,13 @@
       <c r="D35" s="7"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="9">
-        <f>I34-F35+H35</f>
+        <f t="shared" ref="I35:I66" si="3">I34-F35+H35</f>
         <v>0</v>
       </c>
     </row>
@@ -4784,13 +4784,13 @@
       <c r="D36" s="7"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="9">
-        <f>I35-F36+H36</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4801,13 +4801,13 @@
       <c r="D37" s="7"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="9">
-        <f>I36-F37+H37</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4818,13 +4818,13 @@
       <c r="D38" s="7"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="9">
-        <f>I37-F38+H38</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4835,13 +4835,13 @@
       <c r="D39" s="7"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="9">
-        <f>I38-F39+H39</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4852,13 +4852,13 @@
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="9">
-        <f>I39-F40+H40</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4869,13 +4869,13 @@
       <c r="D41" s="7"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="9">
-        <f>I40-F41+H41</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4886,13 +4886,13 @@
       <c r="D42" s="15"/>
       <c r="E42" s="16"/>
       <c r="F42" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="9">
-        <f>I41-F42+H42</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4903,13 +4903,13 @@
       <c r="D43" s="19"/>
       <c r="E43" s="20"/>
       <c r="F43" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G43" s="18"/>
       <c r="H43" s="18"/>
       <c r="I43" s="9">
-        <f>I42-F43+H43</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4920,13 +4920,13 @@
       <c r="D44" s="7"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="6"/>
       <c r="I44" s="9">
-        <f>I43-F44+H44</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4937,13 +4937,13 @@
       <c r="D45" s="7"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G45" s="11"/>
       <c r="H45" s="6"/>
       <c r="I45" s="9">
-        <f>I44-F45+H45</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4954,13 +4954,13 @@
       <c r="D46" s="7"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
       <c r="I46" s="9">
-        <f>I45-F46+H46</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4971,13 +4971,13 @@
       <c r="D47" s="7"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="9">
-        <f>I46-F47+H47</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4988,13 +4988,13 @@
       <c r="D48" s="7"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="9">
-        <f>I47-F48+H48</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5005,13 +5005,13 @@
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="9">
-        <f>I48-F49+H49</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5022,13 +5022,13 @@
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="9">
-        <f>I49-F50+H50</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5039,13 +5039,13 @@
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="9">
-        <f>I50-F51+H51</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5056,13 +5056,13 @@
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
       <c r="I52" s="9">
-        <f>I51-F52+H52</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5073,13 +5073,13 @@
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
       <c r="I53" s="9">
-        <f>I52-F53+H53</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5090,13 +5090,13 @@
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
       <c r="I54" s="9">
-        <f>I53-F54+H54</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5107,13 +5107,13 @@
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
       <c r="I55" s="9">
-        <f>I54-F55+H55</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5124,13 +5124,13 @@
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
       <c r="I56" s="9">
-        <f>I55-F56+H56</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       <c r="G3" s="57"/>
       <c r="H3" s="61"/>
       <c r="I3" s="62">
-        <f>I2-F3+H3</f>
+        <f t="shared" ref="I3:I34" si="0">I2-F3+H3</f>
         <v>-18000</v>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       <c r="G4" s="57"/>
       <c r="H4" s="61"/>
       <c r="I4" s="62">
-        <f>I3-F4+H4</f>
+        <f t="shared" si="0"/>
         <v>-31900</v>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
         <v>31900</v>
       </c>
       <c r="I5" s="62">
-        <f>I4-F5+H5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       <c r="G6" s="58"/>
       <c r="H6" s="61"/>
       <c r="I6" s="62">
-        <f>I5-F6+H6</f>
+        <f t="shared" si="0"/>
         <v>-22000</v>
       </c>
       <c r="J6" s="64"/>
@@ -5326,7 +5326,7 @@
       <c r="G7" s="11"/>
       <c r="H7" s="8"/>
       <c r="I7" s="62">
-        <f>I6-F7+H7</f>
+        <f t="shared" si="0"/>
         <v>-28600</v>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       <c r="D8" s="7"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
-        <f t="shared" ref="F8:F25" si="0">D8*E8</f>
+        <f t="shared" ref="F8:F25" si="1">D8*E8</f>
         <v>0</v>
       </c>
       <c r="G8" s="11">
@@ -5347,7 +5347,7 @@
         <v>28600</v>
       </c>
       <c r="I8" s="9">
-        <f>I7-F8+H8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5358,13 +5358,13 @@
       <c r="D9" s="75"/>
       <c r="E9" s="76"/>
       <c r="F9" s="76">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G9" s="74"/>
       <c r="H9" s="76"/>
       <c r="I9" s="77">
-        <f>I8-F9+H9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       <c r="G10" s="80"/>
       <c r="H10" s="82"/>
       <c r="I10" s="83">
-        <f>I9-F10+H10</f>
+        <f t="shared" si="0"/>
         <v>-19500</v>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       <c r="D11" s="86"/>
       <c r="E11" s="87"/>
       <c r="F11" s="87">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G11" s="88">
@@ -5407,7 +5407,7 @@
         <v>19500</v>
       </c>
       <c r="I11" s="89">
-        <f>I10-F11+H11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       <c r="G12" s="14"/>
       <c r="H12" s="16"/>
       <c r="I12" s="92">
-        <f>I11-F12+H12</f>
+        <f t="shared" si="0"/>
         <v>-18100</v>
       </c>
     </row>
@@ -5442,13 +5442,13 @@
       <c r="D13" s="116"/>
       <c r="E13" s="117"/>
       <c r="F13" s="117">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G13" s="115"/>
       <c r="H13" s="117"/>
       <c r="I13" s="118">
-        <f>I12-F13+H13</f>
+        <f t="shared" si="0"/>
         <v>-18100</v>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       <c r="D14" s="7"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="11">
@@ -5469,7 +5469,7 @@
         <v>18100</v>
       </c>
       <c r="I14" s="9">
-        <f>I13-F14+H14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5480,13 +5480,13 @@
       <c r="D15" s="7"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="8"/>
       <c r="I15" s="9">
-        <f>I14-F15+H15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5497,13 +5497,13 @@
       <c r="D16" s="7"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="8"/>
       <c r="I16" s="9">
-        <f>I15-F16+H16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5514,13 +5514,13 @@
       <c r="D17" s="7"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="8"/>
       <c r="I17" s="9">
-        <f>I16-F17+H17</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5531,13 +5531,13 @@
       <c r="D18" s="7"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="8"/>
       <c r="I18" s="9">
-        <f>I17-F18+H18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5548,13 +5548,13 @@
       <c r="D19" s="7"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="8"/>
       <c r="I19" s="9">
-        <f>I18-F19+H19</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5565,13 +5565,13 @@
       <c r="D20" s="7"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="8"/>
       <c r="I20" s="9">
-        <f>I19-F20+H20</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5582,13 +5582,13 @@
       <c r="D21" s="7"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G21" s="11"/>
       <c r="H21" s="8"/>
       <c r="I21" s="9">
-        <f>I20-F21+H21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5599,13 +5599,13 @@
       <c r="D22" s="7"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="8"/>
       <c r="I22" s="9">
-        <f>I21-F22+H22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5616,13 +5616,13 @@
       <c r="D23" s="7"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="8"/>
       <c r="I23" s="9">
-        <f>I22-F23+H23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5633,13 +5633,13 @@
       <c r="D24" s="7"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="8"/>
       <c r="I24" s="9">
-        <f>I23-F24+H24</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5650,13 +5650,13 @@
       <c r="D25" s="7"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="8"/>
       <c r="I25" s="9">
-        <f>I24-F25+H25</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5667,13 +5667,13 @@
       <c r="D26" s="7"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8">
-        <f t="shared" ref="F26:F58" si="1">C26*E26+D26*E26</f>
+        <f t="shared" ref="F26:F58" si="2">C26*E26+D26*E26</f>
         <v>0</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="8"/>
       <c r="I26" s="9">
-        <f>I25-F26+H26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5684,13 +5684,13 @@
       <c r="D27" s="7"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="8"/>
       <c r="I27" s="9">
-        <f>I26-F27+H27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5701,13 +5701,13 @@
       <c r="D28" s="7"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="8"/>
       <c r="I28" s="9">
-        <f>I27-F28+H28</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5718,13 +5718,13 @@
       <c r="D29" s="7"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="8"/>
       <c r="I29" s="9">
-        <f>I28-F29+H29</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5735,13 +5735,13 @@
       <c r="D30" s="7"/>
       <c r="E30" s="8"/>
       <c r="F30" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="8"/>
       <c r="I30" s="9">
-        <f>I29-F30+H30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5752,13 +5752,13 @@
       <c r="D31" s="7"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="8"/>
       <c r="I31" s="9">
-        <f>I30-F31+H31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5769,13 +5769,13 @@
       <c r="D32" s="7"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="8"/>
       <c r="I32" s="9">
-        <f>I31-F32+H32</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5786,13 +5786,13 @@
       <c r="D33" s="7"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G33" s="11"/>
       <c r="H33" s="8"/>
       <c r="I33" s="9">
-        <f>I32-F33+H33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5803,13 +5803,13 @@
       <c r="D34" s="7"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="8"/>
       <c r="I34" s="9">
-        <f>I33-F34+H34</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5820,13 +5820,13 @@
       <c r="D35" s="7"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9">
-        <f>I34-F35+H35</f>
+        <f t="shared" ref="I35:I66" si="3">I34-F35+H35</f>
         <v>0</v>
       </c>
     </row>
@@ -5837,13 +5837,13 @@
       <c r="D36" s="7"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="8"/>
       <c r="I36" s="9">
-        <f>I35-F36+H36</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5854,13 +5854,13 @@
       <c r="D37" s="7"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="8"/>
       <c r="I37" s="9">
-        <f>I36-F37+H37</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5871,13 +5871,13 @@
       <c r="D38" s="7"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9">
-        <f>I37-F38+H38</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5888,13 +5888,13 @@
       <c r="D39" s="7"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9">
-        <f>I38-F39+H39</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5905,13 +5905,13 @@
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9">
-        <f>I39-F40+H40</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5922,13 +5922,13 @@
       <c r="D41" s="7"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9">
-        <f>I40-F41+H41</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5939,13 +5939,13 @@
       <c r="D42" s="7"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="8"/>
       <c r="I42" s="9">
-        <f>I41-F42+H42</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5956,13 +5956,13 @@
       <c r="D43" s="7"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="8"/>
       <c r="I43" s="9">
-        <f>I42-F43+H43</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5973,13 +5973,13 @@
       <c r="D44" s="15"/>
       <c r="E44" s="16"/>
       <c r="F44" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G44" s="14"/>
       <c r="H44" s="16"/>
       <c r="I44" s="9">
-        <f>I43-F44+H44</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5990,13 +5990,13 @@
       <c r="D45" s="19"/>
       <c r="E45" s="20"/>
       <c r="F45" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G45" s="18"/>
       <c r="H45" s="20"/>
       <c r="I45" s="9">
-        <f>I44-F45+H45</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6007,13 +6007,13 @@
       <c r="D46" s="7"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="8"/>
       <c r="I46" s="9">
-        <f>I45-F46+H46</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6024,13 +6024,13 @@
       <c r="D47" s="7"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G47" s="11"/>
       <c r="H47" s="8"/>
       <c r="I47" s="9">
-        <f>I46-F47+H47</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6041,13 +6041,13 @@
       <c r="D48" s="7"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="8"/>
       <c r="I48" s="9">
-        <f>I47-F48+H48</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6058,13 +6058,13 @@
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="8"/>
       <c r="I49" s="9">
-        <f>I48-F49+H49</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6075,13 +6075,13 @@
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="8"/>
       <c r="I50" s="9">
-        <f>I49-F50+H50</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6092,13 +6092,13 @@
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="8"/>
       <c r="I51" s="9">
-        <f>I50-F51+H51</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6109,13 +6109,13 @@
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="8"/>
       <c r="I52" s="9">
-        <f>I51-F52+H52</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6126,13 +6126,13 @@
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="8"/>
       <c r="I53" s="9">
-        <f>I52-F53+H53</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6143,13 +6143,13 @@
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="8"/>
       <c r="I54" s="9">
-        <f>I53-F54+H54</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6160,13 +6160,13 @@
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="8"/>
       <c r="I55" s="9">
-        <f>I54-F55+H55</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6177,13 +6177,13 @@
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="8"/>
       <c r="I56" s="9">
-        <f>I55-F56+H56</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6194,13 +6194,13 @@
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="8"/>
       <c r="I57" s="9">
-        <f>I56-F57+H57</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6211,13 +6211,13 @@
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="8"/>
       <c r="I58" s="9">
-        <f>I57-F58+H58</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6343,7 +6343,7 @@
       <c r="G3" s="11"/>
       <c r="H3" s="8"/>
       <c r="I3" s="9">
-        <f>I2-F3+H3</f>
+        <f t="shared" ref="I3:I34" si="0">I2-F3+H3</f>
         <v>-10000</v>
       </c>
       <c r="J3" s="130"/>
@@ -6373,7 +6373,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="8"/>
       <c r="I4" s="9">
-        <f>I3-F4+H4</f>
+        <f t="shared" si="0"/>
         <v>-20000</v>
       </c>
       <c r="J4" s="130"/>
@@ -6397,7 +6397,7 @@
         <v>20000</v>
       </c>
       <c r="I5" s="9">
-        <f>I4-F5+H5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J5" s="130"/>
@@ -6431,7 +6431,7 @@
         <v>6000</v>
       </c>
       <c r="I6" s="9">
-        <f>I5-F6+H6</f>
+        <f t="shared" si="0"/>
         <v>3000</v>
       </c>
       <c r="J6" s="130"/>
@@ -6454,7 +6454,7 @@
       <c r="G7" s="106"/>
       <c r="H7" s="8"/>
       <c r="I7" s="9">
-        <f>I6-F7+H7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J7" s="130"/>
@@ -6484,7 +6484,7 @@
       <c r="G8" s="106"/>
       <c r="H8" s="8"/>
       <c r="I8" s="9">
-        <f>I7-F8+H8</f>
+        <f t="shared" si="0"/>
         <v>-3000</v>
       </c>
       <c r="J8" s="130"/>
@@ -6498,7 +6498,7 @@
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
       <c r="F9" s="108">
-        <f t="shared" ref="F9:F16" si="0">D9*E9</f>
+        <f t="shared" ref="F9:F16" si="1">D9*E9</f>
         <v>0</v>
       </c>
       <c r="G9" s="105">
@@ -6508,7 +6508,7 @@
         <v>3000</v>
       </c>
       <c r="I9" s="9">
-        <f>I8-F9+H9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J9" s="178">
@@ -6547,7 +6547,7 @@
         <v>12000</v>
       </c>
       <c r="I10" s="9">
-        <f>I9-F10+H10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J10" s="178">
@@ -6573,7 +6573,7 @@
         <v>1577.5</v>
       </c>
       <c r="E11" s="8">
-        <f t="shared" ref="E11:E14" si="1">F11/D11</f>
+        <f t="shared" ref="E11:E14" si="2">F11/D11</f>
         <v>8.8748019017432647</v>
       </c>
       <c r="F11" s="147">
@@ -6582,7 +6582,7 @@
       <c r="G11" s="106"/>
       <c r="H11" s="8"/>
       <c r="I11" s="9">
-        <f>I10-F11+H11</f>
+        <f t="shared" si="0"/>
         <v>-14000</v>
       </c>
       <c r="J11" s="178"/>
@@ -6601,7 +6601,7 @@
         <v>180</v>
       </c>
       <c r="E12" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>44.444444444444443</v>
       </c>
       <c r="F12" s="147">
@@ -6610,7 +6610,7 @@
       <c r="G12" s="106"/>
       <c r="H12" s="8"/>
       <c r="I12" s="9">
-        <f>I11-F12+H12</f>
+        <f t="shared" si="0"/>
         <v>-22000</v>
       </c>
       <c r="J12" s="178"/>
@@ -6631,7 +6631,7 @@
         <v>40320</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.4404761904761904E-2</v>
       </c>
       <c r="F13" s="147">
@@ -6644,7 +6644,7 @@
         <v>25000</v>
       </c>
       <c r="I13" s="9">
-        <f>I12-F13+H13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J13" s="178">
@@ -6674,7 +6674,7 @@
         <v>1680</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.9523809523809526</v>
       </c>
       <c r="F14" s="147">
@@ -6683,7 +6683,7 @@
       <c r="G14" s="106"/>
       <c r="H14" s="8"/>
       <c r="I14" s="9">
-        <f>I13-F14+H14</f>
+        <f t="shared" si="0"/>
         <v>-10000</v>
       </c>
       <c r="J14" s="178"/>
@@ -6699,7 +6699,7 @@
       <c r="D15" s="15"/>
       <c r="E15" s="16"/>
       <c r="F15" s="108">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G15" s="105">
@@ -6709,7 +6709,7 @@
         <v>10000</v>
       </c>
       <c r="I15" s="9">
-        <f>I14-F15+H15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J15" s="178">
@@ -6730,13 +6730,13 @@
       <c r="D16" s="168"/>
       <c r="E16" s="169"/>
       <c r="F16" s="169">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G16" s="38"/>
       <c r="H16" s="40"/>
       <c r="I16" s="41">
-        <f>I15-F16+H16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J16" s="179"/>
@@ -6766,7 +6766,7 @@
       <c r="G17" s="106"/>
       <c r="H17" s="8"/>
       <c r="I17" s="9">
-        <f>I16-F17+H17</f>
+        <f t="shared" si="0"/>
         <v>-9000</v>
       </c>
       <c r="J17" s="178"/>
@@ -6800,7 +6800,7 @@
         <v>18000</v>
       </c>
       <c r="I18" s="9">
-        <f>I17-F18+H18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J18" s="178">
@@ -6828,7 +6828,7 @@
         <v>25000</v>
       </c>
       <c r="I19" s="9">
-        <f>I18-F19+H19</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J19" s="178">
@@ -6871,14 +6871,14 @@
         <v>32000</v>
       </c>
       <c r="I20" s="9">
-        <f>I19-F20+H20</f>
+        <f t="shared" si="0"/>
         <v>29000</v>
       </c>
       <c r="J20" s="130">
         <v>78000</v>
       </c>
       <c r="K20" s="183">
-        <f t="shared" ref="K20" si="2">J20-H20</f>
+        <f t="shared" ref="K20" si="3">J20-H20</f>
         <v>46000</v>
       </c>
       <c r="L20" s="8"/>
@@ -6899,7 +6899,7 @@
       <c r="G21" s="6"/>
       <c r="H21" s="8"/>
       <c r="I21" s="9">
-        <f>I20-F21+H21</f>
+        <f t="shared" si="0"/>
         <v>14000</v>
       </c>
       <c r="J21" s="130"/>
@@ -6922,7 +6922,7 @@
       <c r="G22" s="6"/>
       <c r="H22" s="8"/>
       <c r="I22" s="9">
-        <f>I21-F22+H22</f>
+        <f t="shared" si="0"/>
         <v>5000</v>
       </c>
       <c r="J22" s="130"/>
@@ -6945,7 +6945,7 @@
       <c r="G23" s="6"/>
       <c r="H23" s="8"/>
       <c r="I23" s="9">
-        <f>I22-F23+H23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J23" s="130"/>
@@ -6970,7 +6970,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="8"/>
       <c r="I24" s="9">
-        <f>I23-F24+H24</f>
+        <f t="shared" si="0"/>
         <v>-8000</v>
       </c>
       <c r="J24" s="130"/>
@@ -6993,7 +6993,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="8"/>
       <c r="I25" s="9">
-        <f>I24-F25+H25</f>
+        <f t="shared" si="0"/>
         <v>-25000</v>
       </c>
       <c r="J25" s="130"/>
@@ -7016,7 +7016,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="8"/>
       <c r="I26" s="9">
-        <f>I25-F26+H26</f>
+        <f t="shared" si="0"/>
         <v>-52000</v>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="8"/>
       <c r="I27" s="9">
-        <f>I26-F27+H27</f>
+        <f t="shared" si="0"/>
         <v>-78000</v>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
         <v>62000</v>
       </c>
       <c r="I28" s="9">
-        <f>I27-F28+H28</f>
+        <f t="shared" si="0"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="8"/>
       <c r="I29" s="9">
-        <f>I28-F29+H29</f>
+        <f t="shared" si="0"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       <c r="G30" s="6"/>
       <c r="H30" s="8"/>
       <c r="I30" s="9">
-        <f>I29-F30+H30</f>
+        <f t="shared" si="0"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7102,7 +7102,7 @@
       <c r="G31" s="11"/>
       <c r="H31" s="8"/>
       <c r="I31" s="9">
-        <f>I30-F31+H31</f>
+        <f t="shared" si="0"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       <c r="G32" s="6"/>
       <c r="H32" s="8"/>
       <c r="I32" s="9">
-        <f>I31-F32+H32</f>
+        <f t="shared" si="0"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       <c r="G33" s="6"/>
       <c r="H33" s="8"/>
       <c r="I33" s="9">
-        <f>I32-F33+H33</f>
+        <f t="shared" si="0"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       <c r="G34" s="6"/>
       <c r="H34" s="8"/>
       <c r="I34" s="9">
-        <f>I33-F34+H34</f>
+        <f t="shared" si="0"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       <c r="G35" s="6"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9">
-        <f>I34-F35+H35</f>
+        <f t="shared" ref="I35:I66" si="4">I34-F35+H35</f>
         <v>-30000</v>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="8"/>
       <c r="I36" s="9">
-        <f>I35-F36+H36</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       <c r="G37" s="6"/>
       <c r="H37" s="8"/>
       <c r="I37" s="9">
-        <f>I36-F37+H37</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       <c r="G38" s="6"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9">
-        <f>I37-F38+H38</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       <c r="G39" s="6"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9">
-        <f>I38-F39+H39</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7225,13 +7225,13 @@
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8">
-        <f t="shared" ref="F40:F56" si="3">C40*E40+D40*E40</f>
+        <f t="shared" ref="F40:F56" si="5">C40*E40+D40*E40</f>
         <v>0</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9">
-        <f>I39-F40+H40</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7242,13 +7242,13 @@
       <c r="D41" s="7"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9">
-        <f>I40-F41+H41</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7259,13 +7259,13 @@
       <c r="D42" s="15"/>
       <c r="E42" s="16"/>
       <c r="F42" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G42" s="14"/>
       <c r="H42" s="16"/>
       <c r="I42" s="9">
-        <f>I41-F42+H42</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7276,13 +7276,13 @@
       <c r="D43" s="19"/>
       <c r="E43" s="20"/>
       <c r="F43" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G43" s="18"/>
       <c r="H43" s="20"/>
       <c r="I43" s="9">
-        <f>I42-F43+H43</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7293,13 +7293,13 @@
       <c r="D44" s="7"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="8"/>
       <c r="I44" s="9">
-        <f>I43-F44+H44</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7310,13 +7310,13 @@
       <c r="D45" s="7"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G45" s="11"/>
       <c r="H45" s="8"/>
       <c r="I45" s="9">
-        <f>I44-F45+H45</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7327,13 +7327,13 @@
       <c r="D46" s="7"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="8"/>
       <c r="I46" s="9">
-        <f>I45-F46+H46</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7344,13 +7344,13 @@
       <c r="D47" s="7"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="8"/>
       <c r="I47" s="9">
-        <f>I46-F47+H47</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7361,13 +7361,13 @@
       <c r="D48" s="7"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="8"/>
       <c r="I48" s="9">
-        <f>I47-F48+H48</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7378,13 +7378,13 @@
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="8"/>
       <c r="I49" s="9">
-        <f>I48-F49+H49</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7395,13 +7395,13 @@
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="8"/>
       <c r="I50" s="9">
-        <f>I49-F50+H50</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7412,13 +7412,13 @@
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="8"/>
       <c r="I51" s="9">
-        <f>I50-F51+H51</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7429,13 +7429,13 @@
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="8"/>
       <c r="I52" s="9">
-        <f>I51-F52+H52</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7446,13 +7446,13 @@
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="8"/>
       <c r="I53" s="9">
-        <f>I52-F53+H53</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7463,13 +7463,13 @@
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="8"/>
       <c r="I54" s="9">
-        <f>I53-F54+H54</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7480,13 +7480,13 @@
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="8"/>
       <c r="I55" s="9">
-        <f>I54-F55+H55</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7497,13 +7497,13 @@
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="8"/>
       <c r="I56" s="9">
-        <f>I55-F56+H56</f>
+        <f t="shared" si="4"/>
         <v>-30000</v>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="8"/>
       <c r="I3" s="9">
-        <f>I2+F3-H3</f>
+        <f t="shared" ref="I3:I24" si="0">I2+F3-H3</f>
         <v>47226</v>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="8"/>
       <c r="I4" s="9">
-        <f>I3+F4-H4</f>
+        <f t="shared" si="0"/>
         <v>73600</v>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
         <v>47226</v>
       </c>
       <c r="I5" s="9">
-        <f>I4+F5-H5</f>
+        <f t="shared" si="0"/>
         <v>26374</v>
       </c>
     </row>
@@ -7683,7 +7683,7 @@
         <v>26374</v>
       </c>
       <c r="I6" s="9">
-        <f>I5+F6-H6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       <c r="G7" s="6"/>
       <c r="H7" s="8"/>
       <c r="I7" s="9">
-        <f>I6+F7-H7</f>
+        <f t="shared" si="0"/>
         <v>36739</v>
       </c>
       <c r="J7" s="12"/>
@@ -7722,7 +7722,7 @@
       <c r="D8" s="7"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
-        <f t="shared" ref="F8:F43" si="0">D8*E8</f>
+        <f t="shared" ref="F8:F43" si="1">D8*E8</f>
         <v>0</v>
       </c>
       <c r="G8" s="11">
@@ -7732,7 +7732,7 @@
         <v>36739</v>
       </c>
       <c r="I8" s="9">
-        <f>I7+F8-H8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
       <c r="G9" s="94"/>
       <c r="H9" s="96"/>
       <c r="I9" s="97">
-        <f>I8+F9-H9</f>
+        <f t="shared" si="0"/>
         <v>48352</v>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       <c r="D10" s="86"/>
       <c r="E10" s="87"/>
       <c r="F10" s="87">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G10" s="98">
@@ -7780,7 +7780,7 @@
         <v>48352</v>
       </c>
       <c r="I10" s="89">
-        <f>I9+F10-H10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
       <c r="G11" s="14"/>
       <c r="H11" s="16"/>
       <c r="I11" s="92">
-        <f>I10+F11-H11</f>
+        <f t="shared" si="0"/>
         <v>48718</v>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       <c r="D12" s="86"/>
       <c r="E12" s="87"/>
       <c r="F12" s="87">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G12" s="88">
@@ -7828,7 +7828,7 @@
         <v>48718</v>
       </c>
       <c r="I12" s="89">
-        <f>I11+F12-H12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       <c r="G13" s="14"/>
       <c r="H13" s="16"/>
       <c r="I13" s="92">
-        <f>I12+F13-H13</f>
+        <f t="shared" si="0"/>
         <v>89843</v>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
       <c r="D14" s="86"/>
       <c r="E14" s="87"/>
       <c r="F14" s="87">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="88">
@@ -7876,7 +7876,7 @@
         <v>89843</v>
       </c>
       <c r="I14" s="89">
-        <f>I13+F14-H14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7903,7 +7903,7 @@
       <c r="G15" s="6"/>
       <c r="H15" s="8"/>
       <c r="I15" s="100">
-        <f>I14+F15-H15</f>
+        <f t="shared" si="0"/>
         <v>142506</v>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       <c r="G16" s="14"/>
       <c r="H16" s="16"/>
       <c r="I16" s="92">
-        <f>I15+F16-H16</f>
+        <f t="shared" si="0"/>
         <v>193814</v>
       </c>
     </row>
@@ -7955,7 +7955,7 @@
       <c r="G17" s="111"/>
       <c r="H17" s="112"/>
       <c r="I17" s="89">
-        <f>I16+F17-H17</f>
+        <f t="shared" si="0"/>
         <v>243646</v>
       </c>
     </row>
@@ -7980,7 +7980,7 @@
       <c r="G18" s="14"/>
       <c r="H18" s="16"/>
       <c r="I18" s="92">
-        <f>I17+F18-H18</f>
+        <f t="shared" si="0"/>
         <v>285898</v>
       </c>
     </row>
@@ -7993,13 +7993,13 @@
       <c r="D19" s="116"/>
       <c r="E19" s="117"/>
       <c r="F19" s="117">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G19" s="115"/>
       <c r="H19" s="117"/>
       <c r="I19" s="118">
-        <f>I18+F19-H19</f>
+        <f t="shared" si="0"/>
         <v>285898</v>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       <c r="D20" s="7"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G20" s="11">
@@ -8020,7 +8020,7 @@
         <v>285898</v>
       </c>
       <c r="I20" s="9">
-        <f>I19+F20-H20</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8033,13 +8033,13 @@
       <c r="D21" s="192"/>
       <c r="E21" s="193"/>
       <c r="F21" s="193">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G21" s="190"/>
       <c r="H21" s="193"/>
       <c r="I21" s="194">
-        <f>I20+F21-H21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       <c r="G22" s="11"/>
       <c r="H22" s="8"/>
       <c r="I22" s="9">
-        <f>I21+F22-H22</f>
+        <f t="shared" si="0"/>
         <v>15000</v>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       <c r="G23" s="6"/>
       <c r="H23" s="8"/>
       <c r="I23" s="9">
-        <f>I22+F23-H23</f>
+        <f t="shared" si="0"/>
         <v>24000</v>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="8"/>
       <c r="I24" s="9">
-        <f>I23+F24-H24</f>
+        <f t="shared" si="0"/>
         <v>34473</v>
       </c>
     </row>
@@ -8121,7 +8121,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="8"/>
       <c r="I25" s="9">
-        <f>I24-F25+H25</f>
+        <f t="shared" ref="I25:I58" si="2">I24-F25+H25</f>
         <v>24554</v>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="8"/>
       <c r="I26" s="9">
-        <f>I25-F26+H26</f>
+        <f t="shared" si="2"/>
         <v>-32075</v>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       <c r="D27" s="7"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G27" s="6" t="s">
@@ -8162,7 +8162,7 @@
         <v>101021</v>
       </c>
       <c r="I27" s="9">
-        <f>I26-F27+H27</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8173,13 +8173,13 @@
       <c r="D28" s="7"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="8"/>
       <c r="I28" s="9">
-        <f>I27-F28+H28</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8190,13 +8190,13 @@
       <c r="D29" s="7"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="8"/>
       <c r="I29" s="9">
-        <f>I28-F29+H29</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8207,13 +8207,13 @@
       <c r="D30" s="7"/>
       <c r="E30" s="8"/>
       <c r="F30" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="8"/>
       <c r="I30" s="9">
-        <f>I29-F30+H30</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8224,13 +8224,13 @@
       <c r="D31" s="7"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="8"/>
       <c r="I31" s="9">
-        <f>I30-F31+H31</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8241,13 +8241,13 @@
       <c r="D32" s="7"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="8"/>
       <c r="I32" s="9">
-        <f>I31-F32+H32</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8258,13 +8258,13 @@
       <c r="D33" s="7"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G33" s="11"/>
       <c r="H33" s="8"/>
       <c r="I33" s="9">
-        <f>I32-F33+H33</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8275,13 +8275,13 @@
       <c r="D34" s="7"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="8"/>
       <c r="I34" s="9">
-        <f>I33-F34+H34</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8292,13 +8292,13 @@
       <c r="D35" s="7"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9">
-        <f>I34-F35+H35</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8309,13 +8309,13 @@
       <c r="D36" s="7"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="8"/>
       <c r="I36" s="9">
-        <f>I35-F36+H36</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8326,13 +8326,13 @@
       <c r="D37" s="7"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="8"/>
       <c r="I37" s="9">
-        <f>I36-F37+H37</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8343,13 +8343,13 @@
       <c r="D38" s="7"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9">
-        <f>I37-F38+H38</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8360,13 +8360,13 @@
       <c r="D39" s="7"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9">
-        <f>I38-F39+H39</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8377,13 +8377,13 @@
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9">
-        <f>I39-F40+H40</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8394,13 +8394,13 @@
       <c r="D41" s="7"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9">
-        <f>I40-F41+H41</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8411,13 +8411,13 @@
       <c r="D42" s="7"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="8"/>
       <c r="I42" s="9">
-        <f>I41-F42+H42</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8428,13 +8428,13 @@
       <c r="D43" s="7"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="8"/>
       <c r="I43" s="9">
-        <f>I42-F43+H43</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8445,13 +8445,13 @@
       <c r="D44" s="15"/>
       <c r="E44" s="16"/>
       <c r="F44" s="16">
-        <f t="shared" ref="F44:F58" si="1">C44*E44+D44*E44</f>
+        <f t="shared" ref="F44:F58" si="3">C44*E44+D44*E44</f>
         <v>0</v>
       </c>
       <c r="G44" s="14"/>
       <c r="H44" s="16"/>
       <c r="I44" s="9">
-        <f>I43-F44+H44</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8462,13 +8462,13 @@
       <c r="D45" s="19"/>
       <c r="E45" s="20"/>
       <c r="F45" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G45" s="18"/>
       <c r="H45" s="20"/>
       <c r="I45" s="9">
-        <f>I44-F45+H45</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8479,13 +8479,13 @@
       <c r="D46" s="7"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="8"/>
       <c r="I46" s="9">
-        <f>I45-F46+H46</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8496,13 +8496,13 @@
       <c r="D47" s="7"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G47" s="11"/>
       <c r="H47" s="8"/>
       <c r="I47" s="9">
-        <f>I46-F47+H47</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8513,13 +8513,13 @@
       <c r="D48" s="7"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="8"/>
       <c r="I48" s="9">
-        <f>I47-F48+H48</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8530,13 +8530,13 @@
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="8"/>
       <c r="I49" s="9">
-        <f>I48-F49+H49</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8547,13 +8547,13 @@
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="8"/>
       <c r="I50" s="9">
-        <f>I49-F50+H50</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8564,13 +8564,13 @@
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="8"/>
       <c r="I51" s="9">
-        <f>I50-F51+H51</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8581,13 +8581,13 @@
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="8"/>
       <c r="I52" s="9">
-        <f>I51-F52+H52</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8598,13 +8598,13 @@
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="8"/>
       <c r="I53" s="9">
-        <f>I52-F53+H53</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8615,13 +8615,13 @@
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="8"/>
       <c r="I54" s="9">
-        <f>I53-F54+H54</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8632,13 +8632,13 @@
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="8"/>
       <c r="I55" s="9">
-        <f>I54-F55+H55</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8649,13 +8649,13 @@
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="8"/>
       <c r="I56" s="9">
-        <f>I55-F56+H56</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8666,13 +8666,13 @@
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="8"/>
       <c r="I57" s="9">
-        <f>I56-F57+H57</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8683,13 +8683,13 @@
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="8"/>
       <c r="I58" s="9">
-        <f>I57-F58+H58</f>
+        <f t="shared" si="2"/>
         <v>68946</v>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       <c r="G3" s="85"/>
       <c r="H3" s="87"/>
       <c r="I3" s="89">
-        <f>I2+F3-H3</f>
+        <f t="shared" ref="I3:I34" si="0">I2+F3-H3</f>
         <v>37440</v>
       </c>
       <c r="J3" s="150">
@@ -8828,7 +8828,7 @@
       <c r="G4" s="94"/>
       <c r="H4" s="96"/>
       <c r="I4" s="122">
-        <f>I3+F4-H4</f>
+        <f t="shared" si="0"/>
         <v>133920</v>
       </c>
     </row>
@@ -8855,7 +8855,7 @@
       <c r="G5" s="88"/>
       <c r="H5" s="87"/>
       <c r="I5" s="89">
-        <f>I4+F5-H5</f>
+        <f t="shared" si="0"/>
         <v>200520</v>
       </c>
       <c r="J5" s="150">
@@ -8879,7 +8879,7 @@
       <c r="G6" s="11"/>
       <c r="H6" s="8"/>
       <c r="I6" s="100">
-        <f>I5+F6-H6</f>
+        <f t="shared" si="0"/>
         <v>229320</v>
       </c>
       <c r="J6" s="27">
@@ -8903,7 +8903,7 @@
       <c r="G7" s="11"/>
       <c r="H7" s="8"/>
       <c r="I7" s="100">
-        <f>I6+F7-H7</f>
+        <f t="shared" si="0"/>
         <v>248520</v>
       </c>
       <c r="J7" s="27">
@@ -8927,7 +8927,7 @@
         <v>25920</v>
       </c>
       <c r="E8" s="8">
-        <f t="shared" ref="E8:E16" si="0">F8/D8</f>
+        <f t="shared" ref="E8:E16" si="1">F8/D8</f>
         <v>4.25</v>
       </c>
       <c r="F8" s="56">
@@ -8936,7 +8936,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="8"/>
       <c r="I8" s="100">
-        <f>I7+F8-H8</f>
+        <f t="shared" si="0"/>
         <v>358680</v>
       </c>
       <c r="J8" s="149"/>
@@ -8953,7 +8953,7 @@
         <v>14400</v>
       </c>
       <c r="E9" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.9166666666666665</v>
       </c>
       <c r="F9" s="56">
@@ -8962,7 +8962,7 @@
       <c r="G9" s="11"/>
       <c r="H9" s="8"/>
       <c r="I9" s="100">
-        <f>I8+F9-H9</f>
+        <f t="shared" si="0"/>
         <v>415080</v>
       </c>
     </row>
@@ -8978,7 +8978,7 @@
         <v>2880</v>
       </c>
       <c r="E10" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.5916666666666668</v>
       </c>
       <c r="F10" s="69">
@@ -8987,7 +8987,7 @@
       <c r="G10" s="14"/>
       <c r="H10" s="16"/>
       <c r="I10" s="92">
-        <f>I9+F10-H10</f>
+        <f t="shared" si="0"/>
         <v>425424</v>
       </c>
     </row>
@@ -9005,7 +9005,7 @@
         <v>8640</v>
       </c>
       <c r="E11" s="87">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.333333333333333</v>
       </c>
       <c r="F11" s="152">
@@ -9014,7 +9014,7 @@
       <c r="G11" s="88"/>
       <c r="H11" s="87"/>
       <c r="I11" s="89">
-        <f>I10+F11-H11</f>
+        <f t="shared" si="0"/>
         <v>462864</v>
       </c>
       <c r="J11" s="150">
@@ -9038,7 +9038,7 @@
         <v>8640</v>
       </c>
       <c r="E12" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.25</v>
       </c>
       <c r="F12" s="155">
@@ -9047,7 +9047,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="8"/>
       <c r="I12" s="100">
-        <f>I11+F12-H12</f>
+        <f t="shared" si="0"/>
         <v>499584</v>
       </c>
       <c r="J12" s="150">
@@ -9069,7 +9069,7 @@
         <v>2880</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.9166666666666665</v>
       </c>
       <c r="F13" s="155">
@@ -9078,7 +9078,7 @@
       <c r="G13" s="11"/>
       <c r="H13" s="8"/>
       <c r="I13" s="100">
-        <f>I12+F13-H13</f>
+        <f t="shared" si="0"/>
         <v>510864</v>
       </c>
       <c r="J13" s="150">
@@ -9102,7 +9102,7 @@
         <v>2880</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.125</v>
       </c>
       <c r="F14" s="8">
@@ -9111,7 +9111,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="8"/>
       <c r="I14" s="100">
-        <f>I13+F14-H14</f>
+        <f t="shared" si="0"/>
         <v>516984</v>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
         <v>5760</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.8395833333333333</v>
       </c>
       <c r="F15" s="8">
@@ -9136,7 +9136,7 @@
       <c r="G15" s="11"/>
       <c r="H15" s="8"/>
       <c r="I15" s="100">
-        <f>I14+F15-H15</f>
+        <f t="shared" si="0"/>
         <v>527580</v>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
         <v>1440</v>
       </c>
       <c r="E16" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.7583333333333337</v>
       </c>
       <c r="F16" s="16">
@@ -9161,7 +9161,7 @@
       <c r="G16" s="14"/>
       <c r="H16" s="16"/>
       <c r="I16" s="92">
-        <f>I15+F16-H16</f>
+        <f t="shared" si="0"/>
         <v>538752</v>
       </c>
     </row>
@@ -9174,13 +9174,13 @@
       <c r="D17" s="116"/>
       <c r="E17" s="117"/>
       <c r="F17" s="117">
-        <f t="shared" ref="F17:F29" si="1">D17*E17</f>
+        <f t="shared" ref="F17:F29" si="2">D17*E17</f>
         <v>0</v>
       </c>
       <c r="G17" s="115"/>
       <c r="H17" s="117"/>
       <c r="I17" s="170">
-        <f>I16+F17-H17</f>
+        <f t="shared" si="0"/>
         <v>538752</v>
       </c>
       <c r="J17" s="149"/>
@@ -9199,7 +9199,7 @@
         <v>2880</v>
       </c>
       <c r="E18" s="8">
-        <f t="shared" ref="E18:E20" si="2">F18/D18</f>
+        <f t="shared" ref="E18:E20" si="3">F18/D18</f>
         <v>6.4652777777777777</v>
       </c>
       <c r="F18" s="8">
@@ -9208,7 +9208,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="8"/>
       <c r="I18" s="100">
-        <f>I17+F18-H18</f>
+        <f t="shared" si="0"/>
         <v>557372</v>
       </c>
     </row>
@@ -9226,7 +9226,7 @@
         <v>4320</v>
       </c>
       <c r="E19" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.416666666666667</v>
       </c>
       <c r="F19" s="54">
@@ -9235,7 +9235,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="8"/>
       <c r="I19" s="100">
-        <f>I18+F19-H19</f>
+        <f t="shared" si="0"/>
         <v>576452</v>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
         <v>7200</v>
       </c>
       <c r="E20" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.25</v>
       </c>
       <c r="F20" s="54">
@@ -9260,7 +9260,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="8"/>
       <c r="I20" s="100">
-        <f>I19+F20-H20</f>
+        <f t="shared" si="0"/>
         <v>643052</v>
       </c>
     </row>
@@ -9282,7 +9282,7 @@
       <c r="G21" s="11"/>
       <c r="H21" s="8"/>
       <c r="I21" s="100">
-        <f>I20+F21-H21</f>
+        <f t="shared" si="0"/>
         <v>656372</v>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       <c r="G22" s="11"/>
       <c r="H22" s="8"/>
       <c r="I22" s="100">
-        <f>I21+F22-H22</f>
+        <f t="shared" si="0"/>
         <v>696944</v>
       </c>
     </row>
@@ -9324,7 +9324,7 @@
       <c r="G23" s="11"/>
       <c r="H23" s="8"/>
       <c r="I23" s="100">
-        <f>I22+F23-H23</f>
+        <f t="shared" si="0"/>
         <v>793424</v>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="8"/>
       <c r="I24" s="100">
-        <f>I23+F24-H24</f>
+        <f t="shared" si="0"/>
         <v>836984</v>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="8"/>
       <c r="I25" s="100">
-        <f>I24+F25-H25</f>
+        <f t="shared" si="0"/>
         <v>849704</v>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="8"/>
       <c r="I26" s="100">
-        <f>I25+F26-H26</f>
+        <f t="shared" si="0"/>
         <v>855944</v>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
         <v>473424</v>
       </c>
       <c r="I27" s="100">
-        <f>I26+F27-H27</f>
+        <f t="shared" si="0"/>
         <v>394520</v>
       </c>
     </row>
@@ -9434,7 +9434,7 @@
       <c r="G28" s="6"/>
       <c r="H28" s="8"/>
       <c r="I28" s="100">
-        <f>I27+F28-H28</f>
+        <f t="shared" si="0"/>
         <v>409040</v>
       </c>
     </row>
@@ -9445,13 +9445,13 @@
       <c r="D29" s="7"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="8"/>
       <c r="I29" s="100">
-        <f>I28+F29-H29</f>
+        <f t="shared" si="0"/>
         <v>409040</v>
       </c>
     </row>
@@ -9462,13 +9462,13 @@
       <c r="D30" s="7"/>
       <c r="E30" s="8"/>
       <c r="F30" s="8">
-        <f t="shared" ref="F30:F59" si="3">C30*E30+D30*E30</f>
+        <f t="shared" ref="F30:F59" si="4">C30*E30+D30*E30</f>
         <v>0</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="8"/>
       <c r="I30" s="100">
-        <f>I29+F30-H30</f>
+        <f t="shared" si="0"/>
         <v>409040</v>
       </c>
     </row>
@@ -9479,13 +9479,13 @@
       <c r="D31" s="7"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="8"/>
       <c r="I31" s="100">
-        <f>I30+F31-H31</f>
+        <f t="shared" si="0"/>
         <v>409040</v>
       </c>
     </row>
@@ -9496,13 +9496,13 @@
       <c r="D32" s="7"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="8"/>
       <c r="I32" s="100">
-        <f>I31+F32-H32</f>
+        <f t="shared" si="0"/>
         <v>409040</v>
       </c>
     </row>
@@ -9513,13 +9513,13 @@
       <c r="D33" s="7"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="8"/>
       <c r="I33" s="100">
-        <f>I32+F33-H33</f>
+        <f t="shared" si="0"/>
         <v>409040</v>
       </c>
     </row>
@@ -9530,13 +9530,13 @@
       <c r="D34" s="7"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="8"/>
       <c r="I34" s="100">
-        <f>I33+F34-H34</f>
+        <f t="shared" si="0"/>
         <v>409040</v>
       </c>
     </row>
@@ -9547,13 +9547,13 @@
       <c r="D35" s="7"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="8"/>
       <c r="I35" s="100">
-        <f>I34+F35-H35</f>
+        <f t="shared" ref="I35:I66" si="5">I34+F35-H35</f>
         <v>409040</v>
       </c>
     </row>
@@ -9564,13 +9564,13 @@
       <c r="D36" s="7"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="8"/>
       <c r="I36" s="100">
-        <f>I35+F36-H36</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9581,13 +9581,13 @@
       <c r="D37" s="7"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="8"/>
       <c r="I37" s="100">
-        <f>I36+F37-H37</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9598,13 +9598,13 @@
       <c r="D38" s="7"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="8"/>
       <c r="I38" s="100">
-        <f>I37+F38-H38</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9615,13 +9615,13 @@
       <c r="D39" s="7"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="8"/>
       <c r="I39" s="100">
-        <f>I38+F39-H39</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9632,13 +9632,13 @@
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="8"/>
       <c r="I40" s="100">
-        <f>I39+F40-H40</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9649,13 +9649,13 @@
       <c r="D41" s="7"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="8"/>
       <c r="I41" s="100">
-        <f>I40+F41-H41</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9666,13 +9666,13 @@
       <c r="D42" s="7"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="8"/>
       <c r="I42" s="100">
-        <f>I41+F42-H42</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9683,13 +9683,13 @@
       <c r="D43" s="7"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="8"/>
       <c r="I43" s="100">
-        <f>I42+F43-H43</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9700,13 +9700,13 @@
       <c r="D44" s="7"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G44" s="6"/>
       <c r="H44" s="8"/>
       <c r="I44" s="100">
-        <f>I43+F44-H44</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9717,13 +9717,13 @@
       <c r="D45" s="15"/>
       <c r="E45" s="16"/>
       <c r="F45" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G45" s="14"/>
       <c r="H45" s="16"/>
       <c r="I45" s="100">
-        <f>I44+F45-H45</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9734,13 +9734,13 @@
       <c r="D46" s="19"/>
       <c r="E46" s="20"/>
       <c r="F46" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G46" s="18"/>
       <c r="H46" s="20"/>
       <c r="I46" s="100">
-        <f>I45+F46-H46</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9751,13 +9751,13 @@
       <c r="D47" s="7"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G47" s="11"/>
       <c r="H47" s="8"/>
       <c r="I47" s="100">
-        <f>I46+F47-H47</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9768,13 +9768,13 @@
       <c r="D48" s="7"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="8"/>
       <c r="I48" s="100">
-        <f>I47+F48-H48</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9785,13 +9785,13 @@
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="8"/>
       <c r="I49" s="100">
-        <f>I48+F49-H49</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9802,13 +9802,13 @@
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="8"/>
       <c r="I50" s="100">
-        <f>I49+F50-H50</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9819,13 +9819,13 @@
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="8"/>
       <c r="I51" s="100">
-        <f>I50+F51-H51</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9836,13 +9836,13 @@
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="8"/>
       <c r="I52" s="100">
-        <f>I51+F52-H52</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9853,13 +9853,13 @@
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="8"/>
       <c r="I53" s="100">
-        <f>I52+F53-H53</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9870,13 +9870,13 @@
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="8"/>
       <c r="I54" s="100">
-        <f>I53+F54-H54</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9887,13 +9887,13 @@
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="8"/>
       <c r="I55" s="100">
-        <f>I54+F55-H55</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9904,13 +9904,13 @@
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="8"/>
       <c r="I56" s="100">
-        <f>I55+F56-H56</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9921,13 +9921,13 @@
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="8"/>
       <c r="I57" s="100">
-        <f>I56+F57-H57</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9938,13 +9938,13 @@
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="8"/>
       <c r="I58" s="100">
-        <f>I57+F58-H58</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
@@ -9955,13 +9955,13 @@
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G59" s="6"/>
       <c r="H59" s="8"/>
       <c r="I59" s="100">
-        <f>I58+F59-H59</f>
+        <f t="shared" si="5"/>
         <v>409040</v>
       </c>
     </row>
